--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494513.3981978873</v>
+        <v>494513</v>
       </c>
       <c r="R2" t="n">
-        <v>6424660.396633678</v>
+        <v>6424660</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2001-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104223</v>
+        <v>104232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104232</v>
+        <v>104235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104235</v>
+        <v>104262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104262</v>
+        <v>104268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104268</v>
+        <v>104275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104275</v>
+        <v>104279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104279</v>
+        <v>104286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104289</v>
+        <v>104294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104294</v>
+        <v>104302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12437-2023 artfynd.xlsx
+++ b/artfynd/A 12437-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222732</v>
       </c>
       <c r="B2" t="n">
-        <v>104302</v>
+        <v>104312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
